--- a/downloads/expense-tracker.xlsx
+++ b/downloads/expense-tracker.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מעקב הוצאות עסק" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'מעקב הוצאות עסק'!$A$1:$F$1,'מעקב הוצאות עסק'!$A$4:$F$24</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -479,9 +481,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -855,110 +857,86 @@
       <c r="F16" s="4" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n"/>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="4" t="n"/>
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>סיכום</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n"/>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="4" t="n"/>
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>סה"כ שכירות</t>
+        </is>
+      </c>
+      <c r="E18" s="9">
+        <f>SUMIF(B5:B16,"שכירות",E5:E16)</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n"/>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="4" t="n"/>
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>סה"כ ציוד</t>
+        </is>
+      </c>
+      <c r="E19" s="9">
+        <f>SUMIF(B5:B16,"ציוד",E5:E16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>סה"כ שיווק</t>
+        </is>
+      </c>
+      <c r="E20" s="9">
+        <f>SUMIF(B5:B16,"שיווק",E5:E16)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>סיכום</t>
-        </is>
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>סה"כ תוכנה</t>
+        </is>
+      </c>
+      <c r="E21" s="9">
+        <f>SUMIF(B5:B16,"תוכנה",E5:E16)</f>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>סה"כ שכירות</t>
+          <t>סה"כ הובלות</t>
         </is>
       </c>
       <c r="E22" s="9">
-        <f>SUMIF(B5:B19,"שכירות",E5:E19)</f>
+        <f>SUMIF(B5:B16,"הובלות",E5:E16)</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>סה"כ ציוד</t>
+          <t>סה"כ אחר</t>
         </is>
       </c>
       <c r="E23" s="9">
-        <f>SUMIF(B5:B19,"ציוד",E5:E19)</f>
+        <f>SUMIF(B5:B16,"אחר",E5:E16)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>סה"כ שיווק</t>
-        </is>
-      </c>
-      <c r="E24" s="9">
-        <f>SUMIF(B5:B19,"שיווק",E5:E19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>סה"כ תוכנה</t>
-        </is>
-      </c>
-      <c r="E25" s="9">
-        <f>SUMIF(B5:B19,"תוכנה",E5:E19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>סה"כ הובלות</t>
-        </is>
-      </c>
-      <c r="E26" s="9">
-        <f>SUMIF(B5:B19,"הובלות",E5:E19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>סה"כ אחר</t>
-        </is>
-      </c>
-      <c r="E27" s="9">
-        <f>SUMIF(B5:B19,"אחר",E5:E19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>סה"כ הוצאות</t>
         </is>
       </c>
-      <c r="E28" s="11">
-        <f>SUM(E5:E19)</f>
+      <c r="E24" s="11">
+        <f>SUM(E5:E16)</f>
         <v/>
       </c>
     </row>
@@ -968,5 +946,6 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/downloads/expense-tracker.xlsx
+++ b/downloads/expense-tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מעקב הוצאות עסק" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'מעקב הוצאות עסק'!$A$1:$F$1,'מעקב הוצאות עסק'!$A$4:$F$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'מעקב הוצאות עסק'!$A$1:$F$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -501,7 +501,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
+    <row r="2" hidden="1" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>מלאו את השורות (התאים הצהובים) — הסיכומים למטה מתעדכנים אוטומטית</t>
